--- a/backend/uploads/csv_template/template.xlsx
+++ b/backend/uploads/csv_template/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vivek\hr chatbot\backend\uploads\csv_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C19E8F-53EA-4238-AAEC-2B302E27F462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F203B72A-4B6E-446A-8317-A68DBF602567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>employee_id</t>
   </si>
@@ -39,9 +39,6 @@
     <t>entity_code</t>
   </si>
   <si>
-    <t>entity_name</t>
-  </si>
-  <si>
     <t>employee_level</t>
   </si>
   <si>
@@ -54,32 +51,29 @@
     <t>John Doe</t>
   </si>
   <si>
-    <t>john.doe@example.com</t>
-  </si>
-  <si>
-    <t>HQ01</t>
-  </si>
-  <si>
-    <t>Headquarters</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
     <t>category</t>
   </si>
   <si>
-    <t>full-time</t>
+    <t>4C</t>
+  </si>
+  <si>
+    <t>FTC</t>
+  </si>
+  <si>
+    <t>ZIL</t>
+  </si>
+  <si>
+    <t>john.doe@adventz.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +84,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -112,14 +114,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -398,15 +403,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,45 +427,42 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{FE5C4B72-134D-45E2-A5BE-537CDE0AD84A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/uploads/csv_template/template.xlsx
+++ b/backend/uploads/csv_template/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vivek\hr chatbot\backend\uploads\csv_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F203B72A-4B6E-446A-8317-A68DBF602567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9715892E-F50D-4F02-8492-688EB4F9DFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>employee_id</t>
   </si>
@@ -67,6 +67,21 @@
   </si>
   <si>
     <t>john.doe@adventz.com</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>EMP002</t>
+  </si>
+  <si>
+    <t>SIL</t>
+  </si>
+  <si>
+    <t>ZMSL</t>
   </si>
 </sst>
 </file>
@@ -403,17 +418,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,13 +446,16 @@
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -453,15 +472,72 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{FE5C4B72-134D-45E2-A5BE-537CDE0AD84A}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{F7645811-B5E3-470B-A2DD-999875386DFB}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{CE13E54F-8A39-4F5E-A8FA-4A27077F94BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/uploads/csv_template/template.xlsx
+++ b/backend/uploads/csv_template/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vivek\hr chatbot\backend\uploads\csv_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9715892E-F50D-4F02-8492-688EB4F9DFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C48A639-625A-4E4D-A4CF-4498A8CA03F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>employee_id</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>ZMSL</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>PE</t>
   </si>
 </sst>
 </file>
@@ -492,17 +498,15 @@
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
@@ -518,10 +522,10 @@
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>15</v>
